--- a/Bin/PrintQR_HC.xlsx
+++ b/Bin/PrintQR_HC.xlsx
@@ -1,30 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ERP SOURCE CODE\Bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C012E6D0-0E43-4AC7-A4A8-C3F67FAC8AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8160" windowHeight="6660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC5E04B2-A0DD-46DE-A69E-5F17A80B965E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="11">
   <si>
     <t>QR</t>
   </si>
@@ -38,23 +50,38 @@
     <t>ExpirationDate</t>
   </si>
   <si>
-    <t>W101000001</t>
+    <t>W209000569</t>
   </si>
   <si>
-    <t>W101000004</t>
+    <t>W209000567</t>
+  </si>
+  <si>
+    <t>W209000565</t>
+  </si>
+  <si>
+    <t>W209000571</t>
+  </si>
+  <si>
+    <t>W209000572</t>
+  </si>
+  <si>
+    <t>W101000002</t>
+  </si>
+  <si>
+    <t>W101000001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,39 +136,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -174,9 +201,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -209,6 +253,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,13 +331,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -285,6 +339,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -349,27 +410,47 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CA5F8A-B967-4A88-A150-AF4A2F66E30B}">
+  <dimension ref="A1:D129"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -383,1432 +464,1796 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2">
-        <v>26050000101</v>
+        <v>26070000117</v>
       </c>
       <c r="B2">
-        <v>26050000101</v>
+        <v>26070000117</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
-        <v>26050000100</v>
+        <v>26070000116</v>
       </c>
       <c r="B3">
-        <v>26050000100</v>
+        <v>26070000116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
-        <v>26050000099</v>
+        <v>26070000115</v>
       </c>
       <c r="B4">
-        <v>26050000099</v>
+        <v>26070000115</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
-        <v>26050000098</v>
+        <v>26070000114</v>
       </c>
       <c r="B5">
-        <v>26050000098</v>
+        <v>26070000114</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
-        <v>26050000097</v>
+        <v>26070000113</v>
       </c>
       <c r="B6">
-        <v>26050000097</v>
+        <v>26070000113</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
-        <v>26050000096</v>
+        <v>26070000112</v>
       </c>
       <c r="B7">
-        <v>26050000096</v>
+        <v>26070000112</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
-        <v>26050000095</v>
+        <v>26070000111</v>
       </c>
       <c r="B8">
-        <v>26050000095</v>
+        <v>26070000111</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
-        <v>26050000094</v>
+        <v>26070000110</v>
       </c>
       <c r="B9">
-        <v>26050000094</v>
+        <v>26070000110</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
-        <v>26050000093</v>
+        <v>26070000109</v>
       </c>
       <c r="B10">
-        <v>26050000093</v>
+        <v>26070000109</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
-        <v>26050000092</v>
+        <v>26070000108</v>
       </c>
       <c r="B11">
-        <v>26050000092</v>
+        <v>26070000108</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
-        <v>26050000091</v>
+        <v>26070000107</v>
       </c>
       <c r="B12">
-        <v>26050000091</v>
+        <v>26070000107</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
-        <v>26050000090</v>
+        <v>26070000106</v>
       </c>
       <c r="B13">
-        <v>26050000090</v>
+        <v>26070000106</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
-        <v>26050000089</v>
+        <v>26070000105</v>
       </c>
       <c r="B14">
-        <v>26050000089</v>
+        <v>26070000105</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
-        <v>26050000088</v>
+        <v>26070000104</v>
       </c>
       <c r="B15">
-        <v>26050000088</v>
+        <v>26070000104</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
-        <v>26050000087</v>
+        <v>26070000103</v>
       </c>
       <c r="B16">
-        <v>26050000087</v>
+        <v>26070000103</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
-        <v>26050000086</v>
+        <v>26070000102</v>
       </c>
       <c r="B17">
-        <v>26050000086</v>
+        <v>26070000102</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
-        <v>26050000085</v>
+        <v>26070000101</v>
       </c>
       <c r="B18">
-        <v>26050000085</v>
+        <v>26070000101</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
-        <v>26050000084</v>
+        <v>26070000100</v>
       </c>
       <c r="B19">
-        <v>26050000084</v>
+        <v>26070000100</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
-        <v>26050000083</v>
+        <v>26070000099</v>
       </c>
       <c r="B20">
-        <v>26050000083</v>
+        <v>26070000099</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
-        <v>26050000082</v>
+        <v>26070000098</v>
       </c>
       <c r="B21">
-        <v>26050000082</v>
+        <v>26070000098</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
-        <v>26050000081</v>
+        <v>26070000097</v>
       </c>
       <c r="B22">
-        <v>26050000081</v>
+        <v>26070000097</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
-        <v>26050000080</v>
+        <v>26070000096</v>
       </c>
       <c r="B23">
-        <v>26050000080</v>
+        <v>26070000096</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
-        <v>26050000079</v>
+        <v>26070000095</v>
       </c>
       <c r="B24">
-        <v>26050000079</v>
+        <v>26070000095</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
-        <v>26050000078</v>
+        <v>26070000094</v>
       </c>
       <c r="B25">
-        <v>26050000078</v>
+        <v>26070000094</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
-        <v>26050000077</v>
+        <v>26070000093</v>
       </c>
       <c r="B26">
-        <v>26050000077</v>
+        <v>26070000093</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
-        <v>26050000076</v>
+        <v>26070000092</v>
       </c>
       <c r="B27">
-        <v>26050000076</v>
+        <v>26070000092</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
-        <v>26050000075</v>
+        <v>26070000091</v>
       </c>
       <c r="B28">
-        <v>26050000075</v>
+        <v>26070000091</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
-        <v>26050000074</v>
+        <v>26070000090</v>
       </c>
       <c r="B29">
-        <v>26050000074</v>
+        <v>26070000090</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
-        <v>26050000073</v>
+        <v>26070000089</v>
       </c>
       <c r="B30">
-        <v>26050000073</v>
+        <v>26070000089</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
-        <v>26050000072</v>
+        <v>26070000088</v>
       </c>
       <c r="B31">
-        <v>26050000072</v>
+        <v>26070000088</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
-        <v>26050000071</v>
+        <v>26070000087</v>
       </c>
       <c r="B32">
-        <v>26050000071</v>
+        <v>26070000087</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
-        <v>26050000070</v>
+        <v>26070000086</v>
       </c>
       <c r="B33">
-        <v>26050000070</v>
+        <v>26070000086</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
-        <v>26050000069</v>
+        <v>26070000085</v>
       </c>
       <c r="B34">
-        <v>26050000069</v>
+        <v>26070000085</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
-        <v>26050000068</v>
+        <v>26070000084</v>
       </c>
       <c r="B35">
-        <v>26050000068</v>
+        <v>26070000084</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
-        <v>26050000067</v>
+        <v>26070000083</v>
       </c>
       <c r="B36">
-        <v>26050000067</v>
+        <v>26070000083</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
-        <v>26050000066</v>
+        <v>26070000082</v>
       </c>
       <c r="B37">
-        <v>26050000066</v>
+        <v>26070000082</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D37" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38">
-        <v>26050000065</v>
+        <v>26070000081</v>
       </c>
       <c r="B38">
-        <v>26050000065</v>
+        <v>26070000081</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
-        <v>26050000064</v>
+        <v>26070000080</v>
       </c>
       <c r="B39">
-        <v>26050000064</v>
+        <v>26070000080</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40">
-        <v>26050000063</v>
+        <v>26070000079</v>
       </c>
       <c r="B40">
-        <v>26050000063</v>
+        <v>26070000079</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41">
-        <v>26050000062</v>
+        <v>26070000078</v>
       </c>
       <c r="B41">
-        <v>26050000062</v>
+        <v>26070000078</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D41" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
-        <v>26050000061</v>
+        <v>26070000077</v>
       </c>
       <c r="B42">
-        <v>26050000061</v>
+        <v>26070000077</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43">
-        <v>26050000060</v>
+        <v>26070000076</v>
       </c>
       <c r="B43">
-        <v>26050000060</v>
+        <v>26070000076</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44">
-        <v>26050000059</v>
+        <v>26070000075</v>
       </c>
       <c r="B44">
-        <v>26050000059</v>
+        <v>26070000075</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D44" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45">
-        <v>26050000058</v>
+        <v>26070000074</v>
       </c>
       <c r="B45">
-        <v>26050000058</v>
+        <v>26070000074</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46">
-        <v>26050000057</v>
+        <v>26070000073</v>
       </c>
       <c r="B46">
-        <v>26050000057</v>
+        <v>26070000073</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47">
-        <v>26050000056</v>
+        <v>26070000072</v>
       </c>
       <c r="B47">
-        <v>26050000056</v>
+        <v>26070000072</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D47" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48">
-        <v>26050000055</v>
+        <v>26070000071</v>
       </c>
       <c r="B48">
-        <v>26050000055</v>
+        <v>26070000071</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D48" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49">
-        <v>26050000054</v>
+        <v>26070000070</v>
       </c>
       <c r="B49">
-        <v>26050000054</v>
+        <v>26070000070</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D49" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50">
-        <v>26050000053</v>
+        <v>26070000069</v>
       </c>
       <c r="B50">
-        <v>26050000053</v>
+        <v>26070000069</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D50" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51">
-        <v>26050000052</v>
+        <v>26070000068</v>
       </c>
       <c r="B51">
-        <v>26050000052</v>
+        <v>26070000068</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D51" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52">
-        <v>26050000051</v>
+        <v>26070000067</v>
       </c>
       <c r="B52">
-        <v>26050000051</v>
+        <v>26070000067</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D52" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53">
-        <v>26050000050</v>
+        <v>26070000066</v>
       </c>
       <c r="B53">
-        <v>26050000050</v>
+        <v>26070000066</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54">
-        <v>26050000049</v>
+        <v>26070000065</v>
       </c>
       <c r="B54">
-        <v>26050000049</v>
+        <v>26070000065</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55">
-        <v>26050000048</v>
+        <v>26070000064</v>
       </c>
       <c r="B55">
-        <v>26050000048</v>
+        <v>26070000064</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56">
-        <v>26050000047</v>
+        <v>26070000063</v>
       </c>
       <c r="B56">
-        <v>26050000047</v>
+        <v>26070000063</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D56" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57">
-        <v>26050000046</v>
+        <v>26070000062</v>
       </c>
       <c r="B57">
-        <v>26050000046</v>
+        <v>26070000062</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D57" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58">
-        <v>26050000045</v>
+        <v>26070000061</v>
       </c>
       <c r="B58">
-        <v>26050000045</v>
+        <v>26070000061</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D58" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59">
-        <v>26050000044</v>
+        <v>26070000060</v>
       </c>
       <c r="B59">
-        <v>26050000044</v>
+        <v>26070000060</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D59" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60">
-        <v>26050000043</v>
+        <v>26070000059</v>
       </c>
       <c r="B60">
-        <v>26050000043</v>
+        <v>26070000059</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D60" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61">
-        <v>26050000042</v>
+        <v>26070000058</v>
       </c>
       <c r="B61">
-        <v>26050000042</v>
+        <v>26070000058</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D61" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62">
-        <v>26050000041</v>
+        <v>26070000057</v>
       </c>
       <c r="B62">
-        <v>26050000041</v>
+        <v>26070000057</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D62" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63">
-        <v>26050000040</v>
+        <v>26070000056</v>
       </c>
       <c r="B63">
-        <v>26050000040</v>
+        <v>26070000056</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D63" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64">
-        <v>26050000039</v>
+        <v>26070000055</v>
       </c>
       <c r="B64">
-        <v>26050000039</v>
+        <v>26070000055</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D64" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65">
-        <v>26050000038</v>
+        <v>26070000054</v>
       </c>
       <c r="B65">
-        <v>26050000038</v>
+        <v>26070000054</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D65" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66">
-        <v>26050000037</v>
+        <v>26070000053</v>
       </c>
       <c r="B66">
-        <v>26050000037</v>
+        <v>26070000053</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D66" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67">
-        <v>26050000036</v>
+        <v>26070000052</v>
       </c>
       <c r="B67">
-        <v>26050000036</v>
+        <v>26070000052</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D67" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68">
-        <v>26050000035</v>
+        <v>26070000051</v>
       </c>
       <c r="B68">
-        <v>26050000035</v>
+        <v>26070000051</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69">
-        <v>26050000034</v>
+        <v>26070000050</v>
       </c>
       <c r="B69">
-        <v>26050000034</v>
+        <v>26070000050</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D69" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70">
-        <v>26050000033</v>
+        <v>26070000049</v>
       </c>
       <c r="B70">
-        <v>26050000033</v>
+        <v>26070000049</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D70" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71">
-        <v>26050000032</v>
+        <v>26070000048</v>
       </c>
       <c r="B71">
-        <v>26050000032</v>
+        <v>26070000048</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D71" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72">
-        <v>26050000031</v>
+        <v>26070000047</v>
       </c>
       <c r="B72">
-        <v>26050000031</v>
+        <v>26070000047</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D72" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73">
-        <v>26050000030</v>
+        <v>26070000046</v>
       </c>
       <c r="B73">
-        <v>26050000030</v>
+        <v>26070000046</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D73" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74">
-        <v>26050000029</v>
+        <v>26070000045</v>
       </c>
       <c r="B74">
-        <v>26050000029</v>
+        <v>26070000045</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D74" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75">
-        <v>26050000028</v>
+        <v>26070000044</v>
       </c>
       <c r="B75">
-        <v>26050000028</v>
+        <v>26070000044</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D75" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76">
-        <v>26050000027</v>
+        <v>26070000043</v>
       </c>
       <c r="B76">
-        <v>26050000027</v>
+        <v>26070000043</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D76" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77">
-        <v>26050000026</v>
+        <v>26070000042</v>
       </c>
       <c r="B77">
-        <v>26050000026</v>
+        <v>26070000042</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D77" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78">
-        <v>26050000025</v>
+        <v>26070000041</v>
       </c>
       <c r="B78">
-        <v>26050000025</v>
+        <v>26070000041</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D78" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79">
-        <v>26050000024</v>
+        <v>26070000040</v>
       </c>
       <c r="B79">
-        <v>26050000024</v>
+        <v>26070000040</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D79" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80">
-        <v>26050000023</v>
+        <v>26070000039</v>
       </c>
       <c r="B80">
-        <v>26050000023</v>
+        <v>26070000039</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D80" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81">
-        <v>26050000022</v>
+        <v>26070000038</v>
       </c>
       <c r="B81">
-        <v>26050000022</v>
+        <v>26070000038</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D81" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82">
-        <v>26050000021</v>
+        <v>26070000037</v>
       </c>
       <c r="B82">
-        <v>26050000021</v>
+        <v>26070000037</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D82" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83">
-        <v>26050000020</v>
+        <v>26070000036</v>
       </c>
       <c r="B83">
-        <v>26050000020</v>
+        <v>26070000036</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D83" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84">
-        <v>26050000019</v>
+        <v>26070000035</v>
       </c>
       <c r="B84">
-        <v>26050000019</v>
+        <v>26070000035</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D84" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85">
-        <v>26050000018</v>
+        <v>26070000034</v>
       </c>
       <c r="B85">
-        <v>26050000018</v>
+        <v>26070000034</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D85" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86">
-        <v>26050000017</v>
+        <v>26070000033</v>
       </c>
       <c r="B86">
-        <v>26050000017</v>
+        <v>26070000033</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D86" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87">
-        <v>26050000016</v>
+        <v>26070000032</v>
       </c>
       <c r="B87">
-        <v>26050000016</v>
+        <v>26070000032</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D87" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88">
-        <v>26050000015</v>
+        <v>26070000031</v>
       </c>
       <c r="B88">
-        <v>26050000015</v>
+        <v>26070000031</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D88" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89">
-        <v>26050000014</v>
+        <v>26070000030</v>
       </c>
       <c r="B89">
-        <v>26050000014</v>
+        <v>26070000030</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D89" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90">
-        <v>26050000013</v>
+        <v>26070000029</v>
       </c>
       <c r="B90">
-        <v>26050000013</v>
+        <v>26070000029</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D90" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91">
-        <v>26050000012</v>
+        <v>26070000028</v>
       </c>
       <c r="B91">
-        <v>26050000012</v>
+        <v>26070000028</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D91" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92">
-        <v>26050000011</v>
+        <v>26070000027</v>
       </c>
       <c r="B92">
-        <v>26050000011</v>
+        <v>26070000027</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D92" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93">
-        <v>26050000010</v>
+        <v>26070000026</v>
       </c>
       <c r="B93">
-        <v>26050000010</v>
+        <v>26070000026</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D93" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94">
-        <v>26050000009</v>
+        <v>26070000025</v>
       </c>
       <c r="B94">
-        <v>26050000009</v>
+        <v>26070000025</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D94" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95">
-        <v>26050000008</v>
+        <v>26070000024</v>
       </c>
       <c r="B95">
-        <v>26050000008</v>
+        <v>26070000024</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D95" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96">
-        <v>26050000007</v>
+        <v>26070000023</v>
       </c>
       <c r="B96">
-        <v>26050000007</v>
+        <v>26070000023</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D96" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97">
-        <v>26050000006</v>
+        <v>26070000022</v>
       </c>
       <c r="B97">
-        <v>26050000006</v>
+        <v>26070000022</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D97" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98">
-        <v>26050000005</v>
+        <v>26070000021</v>
       </c>
       <c r="B98">
-        <v>26050000005</v>
+        <v>26070000021</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D98" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99">
-        <v>26050000004</v>
+        <v>26070000020</v>
       </c>
       <c r="B99">
-        <v>26050000004</v>
+        <v>26070000020</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D99" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100">
-        <v>26050000003</v>
+        <v>26070000019</v>
       </c>
       <c r="B100">
-        <v>26050000003</v>
+        <v>26070000019</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D100" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101">
-        <v>26050000002</v>
+        <v>26070000018</v>
       </c>
       <c r="B101">
-        <v>26050000002</v>
+        <v>26070000018</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D101" s="2">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102">
-        <v>26050000001</v>
+        <v>26070000017</v>
       </c>
       <c r="B102">
-        <v>26050000001</v>
+        <v>26070000017</v>
       </c>
       <c r="C102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103">
+        <v>26070000016</v>
+      </c>
+      <c r="B103">
+        <v>26070000016</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104">
+        <v>26070000015</v>
+      </c>
+      <c r="B104">
+        <v>26070000015</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" s="2">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105">
+        <v>26070000014</v>
+      </c>
+      <c r="B105">
+        <v>26070000014</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="2">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106">
+        <v>26070000013</v>
+      </c>
+      <c r="B106">
+        <v>26070000013</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2">
+        <v>46743</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107">
+        <v>26070000012</v>
+      </c>
+      <c r="B107">
+        <v>26070000012</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108">
+        <v>26070000011</v>
+      </c>
+      <c r="B108">
+        <v>26070000011</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109">
+        <v>26070000010</v>
+      </c>
+      <c r="B109">
+        <v>26070000010</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110">
+        <v>26070000009</v>
+      </c>
+      <c r="B110">
+        <v>26070000009</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111">
+        <v>26070000008</v>
+      </c>
+      <c r="B111">
+        <v>26070000008</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112">
+        <v>26070000007</v>
+      </c>
+      <c r="B112">
+        <v>26070000007</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
+        <v>26070000006</v>
+      </c>
+      <c r="B113">
+        <v>26070000006</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114">
+        <v>26070000005</v>
+      </c>
+      <c r="B114">
+        <v>26070000005</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115">
+        <v>26070000004</v>
+      </c>
+      <c r="B115">
+        <v>26070000004</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116">
+        <v>26070000003</v>
+      </c>
+      <c r="B116">
+        <v>26070000003</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="2">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117">
+        <v>26070000002</v>
+      </c>
+      <c r="B117">
+        <v>26070000002</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D102" s="2">
-        <v>46149</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>26040000001</v>
-      </c>
-      <c r="B103">
-        <v>26040000001</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D103" s="2">
-        <v>46134</v>
+      <c r="D117" s="2">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118">
+        <v>26070000001</v>
+      </c>
+      <c r="B118">
+        <v>26070000001</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="2">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>26060000011</v>
+      </c>
+      <c r="B119">
+        <v>26060000011</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>26060000010</v>
+      </c>
+      <c r="B120">
+        <v>26060000010</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D120" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121">
+        <v>26060000009</v>
+      </c>
+      <c r="B121">
+        <v>26060000009</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122">
+        <v>26060000008</v>
+      </c>
+      <c r="B122">
+        <v>26060000008</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123">
+        <v>26060000007</v>
+      </c>
+      <c r="B123">
+        <v>26060000007</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D123" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124">
+        <v>26060000006</v>
+      </c>
+      <c r="B124">
+        <v>26060000006</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D124" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125">
+        <v>26060000005</v>
+      </c>
+      <c r="B125">
+        <v>26060000005</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126">
+        <v>26060000004</v>
+      </c>
+      <c r="B126">
+        <v>26060000004</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127">
+        <v>26060000003</v>
+      </c>
+      <c r="B127">
+        <v>26060000003</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>26060000002</v>
+      </c>
+      <c r="B128">
+        <v>26060000002</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="2">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129">
+        <v>26060000001</v>
+      </c>
+      <c r="B129">
+        <v>26060000001</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="2">
+        <v>46177</v>
       </c>
     </row>
   </sheetData>
